--- a/event_planner_forms/032_photobooth_events_booking_form--event_planner_forms.xlsx
+++ b/event_planner_forms/032_photobooth_events_booking_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -922,8 +922,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -951,12 +951,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'event_image_type_choice_1',_'label':_'choice_1'}</t>
+          <t>choice_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'event_image_type_choice_1', 'label': 'Choice 1'}</t>
+          <t>Choice 1</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'event_image_type_choice_2',_'label':_'choice_2'}</t>
+          <t>choice_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'event_image_type_choice_2', 'label': 'Choice 2'}</t>
+          <t>Choice 2</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'event_image_type_choice_3',_'label':_'choice_3'}</t>
+          <t>choice_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'event_image_type_choice_3', 'label': 'Choice 3'}</t>
+          <t>Choice 3</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'event_image_type_choice_4',_'label':_'choice_4'}</t>
+          <t>choice_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'event_image_type_choice_4', 'label': 'Choice 4'}</t>
+          <t>Choice 4</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'event_service_choice_1',_'label':_'choice_1'}</t>
+          <t>choice_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'event_service_choice_1', 'label': 'Choice 1'}</t>
+          <t>Choice 1</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'event_service_choice_2',_'label':_'choice_2'}</t>
+          <t>choice_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'event_service_choice_2', 'label': 'Choice 2'}</t>
+          <t>Choice 2</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'event_service_choice_3',_'label':_'choice_3'}</t>
+          <t>choice_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'event_service_choice_3', 'label': 'Choice 3'}</t>
+          <t>Choice 3</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'event_service_choice_4',_'label':_'choice_4'}</t>
+          <t>choice_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'event_service_choice_4', 'label': 'Choice 4'}</t>
+          <t>Choice 4</t>
         </is>
       </c>
     </row>
